--- a/sheets/조재수대금교본/검수/너에게.xlsx
+++ b/sheets/조재수대금교본/검수/너에게.xlsx
@@ -2793,15 +2793,13 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="E12" s="23"/>
@@ -2834,15 +2832,13 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -2851,15 +2847,13 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -2975,15 +2969,13 @@
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="G18" s="24"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="I18" s="24"/>

--- a/sheets/조재수대금교본/검수/너에게.xlsx
+++ b/sheets/조재수대금교본/검수/너에게.xlsx
@@ -2528,20 +2528,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="40.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="44.52" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="44.52" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2594,7 +2594,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="44.52" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="44.52" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="44.52" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="44.52" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       <c r="H8" s="21"/>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="44.52" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="44.52" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="44.52" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="44.52" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="I12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="44.52" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="44.52" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="44.52" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="44.52" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="44.52" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="44.52" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -2986,6 +2986,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>